--- a/workspaces/yzz100407/test_output/bills/内部报告_2024-06.xlsx
+++ b/workspaces/yzz100407/test_output/bills/内部报告_2024-06.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4016,6 +4016,16 @@
           <t>area</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>reading_name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>area_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4051,6 +4061,8 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4082,6 +4094,8 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4113,6 +4127,8 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4141,6 +4157,45 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>新名咖啡</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>shop_renamed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>店铺名称不一致：读数表「旧名咖啡」，面积表「新名咖啡」</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>旧名咖啡</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>新名咖啡</t>
+        </is>
       </c>
     </row>
   </sheetData>
